--- a/astro-site/public/dl/kit-tareas-bar/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/06-eventos-festivos.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Noche Cócteles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Nochevieja" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="After Work" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Maridaje Catas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noche Cócteles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nochevieja" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="After Work" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maridaje Catas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Noche Cócteles'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Nochevieja'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'After Work'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Maridaje Catas'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -132,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -154,59 +159,118 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -566,15 +630,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -582,6 +647,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -603,8 +669,33 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -613,18 +704,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,10 +732,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -669,7 +761,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -684,18 +776,16 @@
           <t xml:space="preserve">  Preparación (48h antes)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -721,10 +811,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -750,10 +838,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -779,10 +865,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -807,24 +891,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Día del Evento</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -850,10 +933,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -879,10 +960,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -908,10 +987,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -937,10 +1014,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -965,6 +1040,8 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
@@ -973,17 +1050,19 @@
       </c>
       <c r="D19" s="19">
         <f>COUNTIF(F5:F17,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F19" s="19" t="n">
-        <v>9</v>
-      </c>
-    </row>
+      <c r="F19" s="19">
+        <f>COUNTIF(B5:B17,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
@@ -991,13 +1070,17 @@
         </is>
       </c>
       <c r="B21" s="15" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="26" t="n"/>
       <c r="E21" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-    </row>
+      <c r="G21" s="26" t="n"/>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
@@ -1015,12 +1098,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1029,18 +1126,18 @@
   <sheetPr>
     <tabColor rgb="00C62828"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1057,10 +1154,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1085,7 +1183,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1100,18 +1198,16 @@
           <t xml:space="preserve">  Planificación</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1137,10 +1233,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1166,10 +1260,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1195,10 +1287,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1224,10 +1314,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1252,24 +1340,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Día de Nochevieja</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1295,10 +1382,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1324,10 +1409,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1353,10 +1436,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1382,10 +1463,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1410,6 +1489,8 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
@@ -1418,17 +1499,19 @@
       </c>
       <c r="D20" s="19">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
-        <v>10</v>
-      </c>
-    </row>
+      <c r="F20" s="19">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
@@ -1436,13 +1519,17 @@
         </is>
       </c>
       <c r="B22" s="15" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="26" t="n"/>
       <c r="E22" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-    </row>
+      <c r="G22" s="26" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
@@ -1460,12 +1547,26 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="F22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1474,18 +1575,18 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1502,10 +1603,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1530,7 +1632,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1545,18 +1647,16 @@
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1582,10 +1682,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1611,10 +1709,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1639,24 +1735,23 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio After-Work</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="23" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1682,10 +1777,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1711,10 +1804,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1740,10 +1831,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1768,6 +1857,8 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
@@ -1776,17 +1867,19 @@
       </c>
       <c r="D17" s="19">
         <f>COUNTIF(F5:F15,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17" s="19" t="n">
-        <v>7</v>
-      </c>
-    </row>
+      <c r="F17" s="19">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
@@ -1794,13 +1887,17 @@
         </is>
       </c>
       <c r="B19" s="15" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="26" t="n"/>
       <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-    </row>
+      <c r="G19" s="26" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
@@ -1818,12 +1915,26 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A17:C17"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F11 F12 F13 F14" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1832,18 +1943,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1860,10 +1971,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1888,7 +2000,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1903,18 +2015,16 @@
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1940,10 +2050,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1969,10 +2077,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1998,10 +2104,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2026,24 +2130,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Evento</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2069,10 +2172,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2098,10 +2199,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2126,6 +2225,8 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
@@ -2134,17 +2235,19 @@
       </c>
       <c r="D17" s="19">
         <f>COUNTIF(F5:F15,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17" s="19" t="n">
-        <v>7</v>
-      </c>
-    </row>
+      <c r="F17" s="19">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
@@ -2152,13 +2255,17 @@
         </is>
       </c>
       <c r="B19" s="15" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="26" t="n"/>
       <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-    </row>
+      <c r="G19" s="26" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
@@ -2176,11 +2283,25 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A17:C17"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-bar/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/06-eventos-festivos.xlsx
@@ -14,10 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maridaje Catas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Noche Cócteles'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Noche Cócteles'!$A$1:$G$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Nochevieja'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Nochevieja'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'After Work'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'After Work'!$A$1:$G$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Maridaje Catas'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Maridaje Catas'!$A$1:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,8 +103,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +153,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3E0"/>
         <bgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -207,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -255,6 +279,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -632,56 +717,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>06 — Eventos y Festivos · Bar / Cocktails</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Checklists para noches especiales y eventos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>▸ Los bares facturan su máximo en noches de evento y temporadas festivas</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>▸ Personaliza con los eventos de tu zona</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Antes de cerrar una cata o un evento privado</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Maridaje Catas» arranca ahora en el momento en que se confirma la reserva, no dos días antes: alérgenos e intolerancias por escrito, precio por persona y qué incluye, señal cobrada, política de cancelación y plazo para el número final de asistentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>▸ Los alérgenos también van en la barra del día a día: la carta de cócteles los declara en «Coctelería Clásica» (02) y los snacks de cortesía del after-work, en su propia hoja. Que un producto sea gratis o sea una bebida no exime de informar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>▸ Estás en 06-eventos-festivos.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="35" customHeight="1">
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -706,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -728,7 +968,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -756,7 +996,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -771,340 +1011,393 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Preparación (48h antes)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Diseñar menú de cócteles especiales (4-6 cócteles)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Calcular ingredientes necesarios y hacer pedidos extra</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Preparar infusiones, cordials o jarabes especiales</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>24h antes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Publicar evento en RRSS con fotos de cócteles</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="n"/>
+      <c r="B10" s="40" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="40" t="n"/>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="40" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  Día del Evento</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="26" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="33" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Preparar batches de cócteles especiales</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Preparar garnish especial (deshidratados, flores comestibles, espuma)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Imprimir menú especial / colocar en mesas</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Reforzar equipo (bartender extra, barback extra)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Apertura</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Stock extra de hielo (50% más que un día normal)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D19" s="19">
-        <f>COUNTIF(F5:F17,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F19" s="19">
-        <f>COUNTIF(B5:B17,"?*")</f>
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="26" t="n"/>
+      <c r="A21" s="42" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D23" s="19">
+        <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23" s="19">
+        <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="26" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G17">
+  <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1128,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1443,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1471,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1193,367 +1486,420 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Planificación</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Definir concepto de la noche (fiesta, cena + barra libre, precio entrada)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>3 sem antes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Calcular stock necesario (3-4x un viernes normal)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>2 sem antes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Contratar personal extra</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>2 sem antes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Preparar decoración especial</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>1 sem antes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Preparar uvas y cava/champagne para las 12</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>Día antes</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  Día de Nochevieja</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Stock masivo de hielo</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Preparar batches de cócteles de alta rotación</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Preparar botellas de champagne/cava en hielo</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Servir cava a medianoche</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Todo equipo</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Gestionar aforo y seguridad</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="19">
-        <f>COUNTIF(F5:F18,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F20" s="19">
-        <f>COUNTIF(B5:B18,"?*")</f>
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="26" t="n"/>
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D24" s="19">
+        <f>COUNTIFS(B5:B22,"?*",F5:F22,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F24" s="19">
+        <f>COUNTIF(B5:B22,"?*")-COUNTIF(F5:F22,"N/A")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="26" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G22">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1577,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1627,7 +1973,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1642,286 +1988,366 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Definir horario de happy hour (ej. 18:00-20:00)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Fijo</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Definir carta reducida de cócteles con descuento</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>Fijo</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Publicar en RRSS y colocar pizarra en la entrada</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>Diario</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="n"/>
+      <c r="B9" s="40" t="n"/>
+      <c r="C9" s="40" t="n"/>
+      <c r="D9" s="40" t="n"/>
+      <c r="E9" s="40" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="40" t="n"/>
+    </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio After-Work</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="25" t="n"/>
-      <c r="G10" s="26" t="n"/>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Preparar batches de cócteles de happy hour</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Preparar snacks / tapas de cortesía (si aplica)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Tener por escrito los alérgenos de los snacks y las tapas de cortesía y que el equipo sepa dónde consultarlos: que sean gratis no exime de informar</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Servicio rápido: objetivo &lt;2 min por cóctel</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Mantener música y ambiente apropiados para after-work</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="n"/>
+      <c r="B16" s="43" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="42" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D17" s="19">
-        <f>COUNTIF(F5:F15,"✓")</f>
+      <c r="D22" s="19">
+        <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17" s="19">
-        <f>COUNTIF(B5:B15,"?*")</f>
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="F22" s="19">
+        <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="B24" s="44" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="26" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="F24" s="44" t="n"/>
+      <c r="G24" s="26" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
-    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A17:C17"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G15">
+  <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1945,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1967,7 +2393,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1995,7 +2421,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2010,286 +2436,497 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AL CONFIRMAR LA RESERVA</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Recoger POR ESCRITO alérgenos, intolerancias y dietas de los asistentes y trasladarlos a la barra y a quien prepare la comida del maridaje (en una cata, frutos secos y sulfitos son los dos que siempre aparecen)</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Cerrar por escrito el precio por persona y qué incluye: número de piezas, maridaje de comida, copa de despedida y si hay botella para llevar</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Cobrar la señal o el anticipo y dejar constancia del importe y la fecha</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Firmar la política de cancelación y el plazo para dar el número final de asistentes</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Acordar la hora de entrada y de salida del espacio y quién monta y desmonta la sala</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Seleccionar 4-6 piezas para cata (vinos, spirits, cócteles)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>1 sem antes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Preparar fichas de cata para clientes</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>3 días antes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Confirmar asistentes y preparar sala</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>1 día antes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Preparar maridaje food (quesos, chocolates, tapas)</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Preparar la comida del maridaje (quesos, chocolates y tapas)</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="40" t="n"/>
+      <c r="D17" s="40" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="40" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  Evento</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="26" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="33" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Presentar cada pieza: historia, notas de cata, técnica</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Servir en copa/vaso correcto</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Gestionar ritmo de la cata (15-20 min por pieza)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="39" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D17" s="19">
-        <f>COUNTIF(F5:F15,"✓")</f>
+      <c r="D28" s="19">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17" s="19">
-        <f>COUNTIF(B5:B15,"?*")</f>
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="F28" s="19">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="26" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="F30" s="44" t="n"/>
+      <c r="G30" s="26" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F19:G19"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G15">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
